--- a/sc0_match_results.xlsx
+++ b/sc0_match_results.xlsx
@@ -821,21 +821,21 @@
     <t>Kevin Clancy</t>
   </si>
   <si>
+    <t>Steven McLean</t>
+  </si>
+  <si>
     <t>Euan Anderson</t>
   </si>
   <si>
+    <t>Lloyd Wilson</t>
+  </si>
+  <si>
     <t>Ross Hardie</t>
   </si>
   <si>
     <t>Grant Irvine</t>
   </si>
   <si>
-    <t>Steven McLean</t>
-  </si>
-  <si>
-    <t>Lloyd Wilson</t>
-  </si>
-  <si>
     <t>John Beaton</t>
   </si>
   <si>
@@ -884,21 +884,21 @@
     <t>https://fbref.com/en/matches/e6554fa2/St-Johnstone-Aberdeen-August-5-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b8e6969e/St-Mirren-St-Johnstone-October-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/243c9ff0/Heart-of-Midlothian-Kilmarnock-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fb394c66/Dundee-United-Motherwell-October-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5e06d4fa/Celtic-Dundee-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/9066db1d/Ross-County-Hibernian-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b8e6969e/St-Mirren-St-Johnstone-October-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fb394c66/Dundee-United-Motherwell-October-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2bc330fa/Aberdeen-Rangers-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -911,24 +911,24 @@
     <t>https://fbref.com/en/matches/7b93868a/Hibernian-Aberdeen-November-26-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3da36d25/Celtic-Dundee-United-January-8-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/308f66e0/Kilmarnock-Motherwell-January-8-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3da36d25/Celtic-Dundee-United-January-8-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9b632d5a/Dundee-Rangers-January-9-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8fb2341b/Hibernian-St-Mirren-November-9-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/37bdcada/Dundee-United-Ross-County-November-9-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0ca6d764/Motherwell-St-Johnstone-November-9-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/37bdcada/Dundee-United-Ross-County-November-9-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8fb2341b/Hibernian-St-Mirren-November-9-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fddc2b46/Aberdeen-Dundee-November-9-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -938,12 +938,12 @@
     <t>https://fbref.com/en/matches/ea1763a1/Rangers-Heart-of-Midlothian-November-10-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4c5a8bca/Ross-County-Motherwell-November-23-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2599fc31/St-Johnstone-Kilmarnock-November-23-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4c5a8bca/Ross-County-Motherwell-November-23-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1aaa7ff5/Rangers-Dundee-United-November-23-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -956,18 +956,18 @@
     <t>https://fbref.com/en/matches/40327842/Heart-of-Midlothian-Celtic-November-23-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4c74869f/Celtic-Ross-County-November-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/984b304b/Motherwell-Hibernian-November-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e61740ec/Dundee-United-St-Mirren-November-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2316c31e/Kilmarnock-Dundee-November-30-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4c74869f/Celtic-Ross-County-November-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/984b304b/Motherwell-Hibernian-November-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e61740ec/Dundee-United-St-Mirren-November-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/32ef90a0/St-Johnstone-Rangers-December-1-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -995,27 +995,27 @@
     <t>https://fbref.com/en/matches/32dd944a/Heart-of-Midlothian-Dundee-December-7-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bc87d012/St-Mirren-Motherwell-December-7-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/da6ed2c3/Celtic-Hibernian-December-7-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d042afb3/Aberdeen-St-Johnstone-December-7-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/912d8208/Dundee-United-Kilmarnock-December-7-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bc87d012/St-Mirren-Motherwell-December-7-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d042afb3/Aberdeen-St-Johnstone-December-7-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/da6ed2c3/Celtic-Hibernian-December-7-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/33bc939b/Ross-County-Rangers-December-8-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7c8f9957/Hibernian-Ross-County-December-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1ebb323f/St-Johnstone-St-Mirren-December-14-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7c8f9957/Hibernian-Ross-County-December-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/94d0e535/Motherwell-Dundee-United-December-14-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -1052,15 +1052,15 @@
     <t>https://fbref.com/en/matches/2d98e4f1/St-Johnstone-Dundee-United-December-26-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3d045017/Celtic-Motherwell-December-26-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fa3d2759/Dundee-Ross-County-December-26-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/377cdd1e/Kilmarnock-Aberdeen-December-26-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3d045017/Celtic-Motherwell-December-26-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fa3d2759/Dundee-Ross-County-December-26-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e532f712/St-Mirren-Rangers-December-26-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -1088,33 +1088,33 @@
     <t>https://fbref.com/en/matches/7c89743b/St-Mirren-Dundee-December-29-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9d62990c/Hibernian-Kilmarnock-December-29-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/88614304/Motherwell-Rangers-December-29-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7e37ddf0/Ross-County-Heart-of-Midlothian-December-29-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/88614304/Motherwell-Rangers-December-29-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9d62990c/Hibernian-Kilmarnock-December-29-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e83b0ccb/Dundee-United-Aberdeen-December-29-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e9c07aa0/Kilmarnock-St-Mirren-January-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/05f4ed4c/Old-Firm-Derby-Rangers-Celtic-January-2-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/cea70176/Aberdeen-Ross-County-January-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/940ef160/Heart-of-Midlothian-Motherwell-January-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/840ef9c9/St-Johnstone-Hibernian-January-2-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/940ef160/Heart-of-Midlothian-Motherwell-January-2-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/cea70176/Aberdeen-Ross-County-January-2-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e9c07aa0/Kilmarnock-St-Mirren-January-2-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/372f087d/Dundee-Dundee-United-January-2-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -1124,6 +1124,9 @@
     <t>https://fbref.com/en/matches/e6e0081b/Motherwell-Aberdeen-January-5-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/edbffc0c/Kilmarnock-Ross-County-January-5-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1c66a7c9/Celtic-St-Mirren-January-5-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -1133,9 +1136,6 @@
     <t>https://fbref.com/en/matches/9b7e92cb/St-Johnstone-Dundee-January-5-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/edbffc0c/Kilmarnock-Ross-County-January-5-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c1b32f12/Dundee-Kilmarnock-November-3-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -1148,39 +1148,39 @@
     <t>https://fbref.com/en/matches/e2a8d725/Hibernian-Motherwell-January-11-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a02065d3/Rangers-St-Johnstone-January-12-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/78f14c19/Aberdeen-Heart-of-Midlothian-January-12-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a02065d3/Rangers-St-Johnstone-January-12-2025-Scottish-Premiership</t>
+    <t>https://fbref.com/en/matches/d79cd451/Aberdeen-St-Mirren-January-25-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e531ac9a/Heart-of-Midlothian-Kilmarnock-January-25-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/90014a11/St-Johnstone-Motherwell-January-25-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3637272e/Ross-County-Hibernian-January-25-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/90014a11/St-Johnstone-Motherwell-January-25-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d79cd451/Aberdeen-St-Mirren-January-25-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e531ac9a/Heart-of-Midlothian-Kilmarnock-January-25-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/30670ab2/Dundee-United-Rangers-January-26-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/66f78d4e/Celtic-Dundee-February-5-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3ad7bc5e/Hibernian-Aberdeen-February-1-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0757dc49/St-Mirren-St-Johnstone-February-1-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/300f7d2e/Dundee-Heart-of-Midlothian-February-1-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3ad7bc5e/Hibernian-Aberdeen-February-1-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8cd0becf/Kilmarnock-Dundee-United-February-1-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -1190,18 +1190,18 @@
     <t>https://fbref.com/en/matches/a56e29c2/Rangers-Ross-County-February-2-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d5d17424/Kilmarnock-St-Johnstone-February-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6ec02fb0/Dundee-Aberdeen-February-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d0ae9d90/Motherwell-Ross-County-February-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6a1f684d/Celtic-Dundee-United-February-15-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6ec02fb0/Dundee-Aberdeen-February-15-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d0ae9d90/Motherwell-Ross-County-February-15-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d5d17424/Kilmarnock-St-Johnstone-February-15-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ec8d1ecf/Heart-of-Midlothian-Rangers-February-16-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -1211,18 +1211,18 @@
     <t>https://fbref.com/en/matches/0b62e5ac/Hibernian-Celtic-February-22-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ea261585/Aberdeen-Kilmarnock-February-22-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cb800241/Dundee-United-Motherwell-February-22-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3755a2f2/Rangers-St-Mirren-February-22-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a4110188/Ross-County-Dundee-February-22-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cb800241/Dundee-United-Motherwell-February-22-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ea261585/Aberdeen-Kilmarnock-February-22-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/baa42a3b/St-Johnstone-Heart-of-Midlothian-February-23-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -1244,22 +1244,22 @@
     <t>https://fbref.com/en/matches/1e557ac5/Kilmarnock-Rangers-February-26-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bd56f1be/Dundee-St-Johnstone-March-1-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/50f69ff9/Rangers-Motherwell-March-1-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bd56f1be/Dundee-St-Johnstone-March-1-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ea15fb4e/Ross-County-Kilmarnock-March-1-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5dd5b07f/St-Mirren-Celtic-March-1-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/f3aacc58/7c77b0bc/Hibernian-vs-Heart-of-Midlothian-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/e986ece7/8bbab7cf/Dundee-United-vs-Aberdeen-History</t>
+    <t>https://fbref.com/en/matches/1d333832/Hibernian-Heart-of-Midlothian-March-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/995a849b/Aberdeen-Dundee-United-March-2-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/94ab474a/Hibernian-Dundee-August-24-2024-Scottish-Premiership</t>
@@ -1274,147 +1274,147 @@
     <t>https://fbref.com/en/matches/9dc2d830/St-Mirren-Celtic-August-25-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a0f450ae/Motherwell-Heart-of-Midlothian-August-25-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7df69c15/Aberdeen-Kilmarnock-August-25-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a0f450ae/Motherwell-Heart-of-Midlothian-August-25-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/9d04848a/3568ad4c/Motherwell-vs-St-Mirren-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/dd289621/8bbab7cf/St-Johnstone-vs-Aberdeen-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/f3aacc58/25f1fd26/Hibernian-vs-Kilmarnock-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/a5298e9f/7c77b0bc/Ross-County-vs-Heart-of-Midlothian-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/b81aa4fa/86b7acd2/Old-Firm-Derby-Celtic-vs-Rangers-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/e986ece7/00032902/Dundee-United-vs-Dundee-History</t>
+    <t>https://fbref.com/en/matches/a427092f/Heart-of-Midlothian-Ross-County-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a3316909/Kilmarnock-Hibernian-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/908b7821/St-Johnstone-Aberdeen-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8615de15/Motherwell-St-Mirren-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9457d08f/Old-Firm-Derby-Celtic-Rangers-March-16-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2a374a4/Dundee-United-Dundee-March-16-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/3568ad4c/25f1fd26/St-Mirren-vs-Kilmarnock-History</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/b81aa4fa/7c77b0bc/Celtic-vs-Heart-of-Midlothian-History</t>
   </si>
   <si>
     <t>https://fbref.com/en/stathead/matchup/teams/f3aacc58/dd289621/Hibernian-vs-St-Johnstone-History</t>
   </si>
   <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/9d04848a/8bbab7cf/Motherwell-vs-Aberdeen-History</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/86b7acd2/00032902/Rangers-vs-Dundee-History</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/stathead/matchup/teams/e986ece7/a5298e9f/Dundee-United-vs-Ross-County-History</t>
   </si>
   <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/3568ad4c/25f1fd26/St-Mirren-vs-Kilmarnock-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/9d04848a/8bbab7cf/Motherwell-vs-Aberdeen-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/86b7acd2/00032902/Rangers-vs-Dundee-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/b81aa4fa/7c77b0bc/Celtic-vs-Heart-of-Midlothian-History</t>
+    <t>https://fbref.com/en/stathead/matchup/teams/3568ad4c/00032902/St-Mirren-vs-Dundee-History</t>
   </si>
   <si>
     <t>https://fbref.com/en/stathead/matchup/teams/f3aacc58/86b7acd2/Hibernian-vs-Rangers-History</t>
   </si>
   <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/9d04848a/25f1fd26/Motherwell-vs-Kilmarnock-History</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/a5298e9f/8bbab7cf/Ross-County-vs-Aberdeen-History</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/stathead/matchup/teams/dd289621/b81aa4fa/St-Johnstone-vs-Celtic-History</t>
   </si>
   <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/a5298e9f/8bbab7cf/Ross-County-vs-Aberdeen-History</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/stathead/matchup/teams/e986ece7/7c77b0bc/Dundee-United-vs-Heart-of-Midlothian-History</t>
   </si>
   <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/3568ad4c/00032902/St-Mirren-vs-Dundee-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/9d04848a/25f1fd26/Motherwell-vs-Kilmarnock-History</t>
+    <t>https://fbref.com/en/stathead/matchup/teams/a5298e9f/3568ad4c/Ross-County-vs-St-Mirren-History</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/b81aa4fa/25f1fd26/Celtic-vs-Kilmarnock-History</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/e986ece7/dd289621/Dundee-United-vs-St-Johnstone-History</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/9d04848a/7c77b0bc/Motherwell-vs-Heart-of-Midlothian-History</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/stathead/matchup/teams/8bbab7cf/86b7acd2/Aberdeen-vs-Rangers-History</t>
   </si>
   <si>
     <t>https://fbref.com/en/stathead/matchup/teams/f3aacc58/00032902/Hibernian-vs-Dundee-History</t>
   </si>
   <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/8bbab7cf/86b7acd2/Aberdeen-vs-Rangers-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/9d04848a/7c77b0bc/Motherwell-vs-Heart-of-Midlothian-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/e986ece7/dd289621/Dundee-United-vs-St-Johnstone-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/b81aa4fa/25f1fd26/Celtic-vs-Kilmarnock-History</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/stathead/matchup/teams/a5298e9f/3568ad4c/Ross-County-vs-St-Mirren-History</t>
+    <t>https://fbref.com/en/matches/8254a65d/St-Johnstone-Motherwell-August-31-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/30131e2c/Dundee-St-Mirren-August-31-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8254a65d/St-Johnstone-Motherwell-August-31-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b15c46f2/Ross-County-Aberdeen-August-31-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/20a083c1/Old-Firm-Derby-Celtic-Rangers-September-1-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f669adee/Kilmarnock-Hibernian-September-1-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5e8392ec/Heart-of-Midlothian-Dundee-United-September-1-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f669adee/Kilmarnock-Hibernian-September-1-2024-Scottish-Premiership</t>
+    <t>https://fbref.com/en/matches/4d21a7b4/Ross-County-Dundee-September-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/428dec43/Aberdeen-Motherwell-September-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/56bfe1e9/Hibernian-St-Johnstone-September-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8f673980/Celtic-Heart-of-Midlothian-September-14-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/15ed5511/St-Mirren-Kilmarnock-September-14-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/428dec43/Aberdeen-Motherwell-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/4d21a7b4/Ross-County-Dundee-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/56bfe1e9/Hibernian-St-Johnstone-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8f673980/Celtic-Heart-of-Midlothian-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/77c13f3b/Dundee-United-Rangers-September-15-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d3bc079b/Kilmarnock-Dundee-United-September-28-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/9efd8a62/Heart-of-Midlothian-Ross-County-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d3bc079b/Kilmarnock-Dundee-United-September-28-2024-Scottish-Premiership</t>
+    <t>https://fbref.com/en/matches/ed92dd8c/Dundee-Aberdeen-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d7b2ed59/Motherwell-St-Mirren-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ed92dd8c/Dundee-Aberdeen-September-28-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a30220aa/St-Johnstone-Celtic-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/fdb926ed/Rangers-Hibernian-September-29-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b6b34b08/Dundee-Kilmarnock-October-5-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1bd44a80/St-Mirren-Dundee-United-October-5-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/91abdab9/Hibernian-Motherwell-October-5-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b6b34b08/Dundee-Kilmarnock-October-5-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/519d3fb9/Ross-County-Celtic-October-6-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -1424,28 +1424,28 @@
     <t>https://fbref.com/en/matches/1b839ace/Rangers-St-Johnstone-October-6-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3bd671ec/St-Johnstone-Ross-County-October-19-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3c3fa65d/Heart-of-Midlothian-St-Mirren-October-19-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b89ef4e2/Celtic-Aberdeen-October-19-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/168d4a08/Motherwell-Dundee-October-19-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3bd671ec/St-Johnstone-Ross-County-October-19-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3c3fa65d/Heart-of-Midlothian-St-Mirren-October-19-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b89ef4e2/Celtic-Aberdeen-October-19-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d4e66239/Dundee-United-Hibernian-October-19-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/62a8b15b/Kilmarnock-Rangers-October-20-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d1729397/Ross-County-Kilmarnock-October-26-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/18f3e515/Dundee-St-Johnstone-October-26-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d1729397/Ross-County-Kilmarnock-October-26-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/41db5901/Aberdeen-Dundee-United-October-26-2024-Scottish-Premiership</t>
@@ -1952,22 +1952,22 @@
         <v>231</v>
       </c>
       <c r="K8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.0</v>
       </c>
-      <c r="M8" t="s">
-        <v>250</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.0</v>
-      </c>
       <c r="O8" t="n">
-        <v>18402.0</v>
+        <v>6042.0</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q8" t="s">
         <v>269</v>
@@ -2011,22 +2011,22 @@
         <v>231</v>
       </c>
       <c r="K9" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="L9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>250</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.0</v>
       </c>
-      <c r="M9" t="s">
-        <v>251</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.0</v>
-      </c>
       <c r="O9" t="n">
-        <v>58751.0</v>
+        <v>18402.0</v>
       </c>
       <c r="P9" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Q9" t="s">
         <v>270</v>
@@ -2070,22 +2070,22 @@
         <v>231</v>
       </c>
       <c r="K10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M10" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O10" t="n">
-        <v>3468.0</v>
+        <v>8415.0</v>
       </c>
       <c r="P10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Q10" t="s">
         <v>271</v>
@@ -2129,22 +2129,22 @@
         <v>231</v>
       </c>
       <c r="K11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L11" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="N11" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O11" t="n">
-        <v>6042.0</v>
+        <v>58751.0</v>
       </c>
       <c r="P11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q11" t="s">
         <v>272</v>
@@ -2188,22 +2188,22 @@
         <v>231</v>
       </c>
       <c r="K12" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M12" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N12" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O12" t="n">
-        <v>8415.0</v>
+        <v>3468.0</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q12" t="s">
         <v>273</v>
@@ -2483,25 +2483,25 @@
         <v>231</v>
       </c>
       <c r="K17" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N17" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" t="n">
-        <v>4601.0</v>
+        <v>28647.0</v>
       </c>
       <c r="P17" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Q17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R17" t="e">
         <v>#N/A</v>
@@ -2542,25 +2542,25 @@
         <v>231</v>
       </c>
       <c r="K18" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N18" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" t="n">
-        <v>28647.0</v>
+        <v>4601.0</v>
       </c>
       <c r="P18" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R18" t="e">
         <v>#N/A</v>
@@ -2660,25 +2660,25 @@
         <v>227</v>
       </c>
       <c r="K20" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="L20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>244</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.0</v>
       </c>
-      <c r="M20" t="s">
-        <v>246</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O20" t="n">
-        <v>4306.0</v>
+        <v>15594.0</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="Q20" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="R20" t="e">
         <v>#N/A</v>
@@ -2778,25 +2778,25 @@
         <v>227</v>
       </c>
       <c r="K22" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="L22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>246</v>
+      </c>
+      <c r="N22" t="n">
         <v>1.0</v>
       </c>
-      <c r="M22" t="s">
-        <v>244</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.0</v>
-      </c>
       <c r="O22" t="n">
-        <v>15594.0</v>
+        <v>4306.0</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="Q22" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="R22" t="e">
         <v>#N/A</v>
@@ -3014,25 +3014,25 @@
         <v>227</v>
       </c>
       <c r="K26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L26" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>242</v>
+      </c>
+      <c r="N26" t="n">
         <v>1.0</v>
       </c>
-      <c r="M26" t="s">
-        <v>250</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.0</v>
-      </c>
       <c r="O26" t="n">
-        <v>1872.0</v>
+        <v>3410.0</v>
       </c>
       <c r="P26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q26" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="R26" t="e">
         <v>#N/A</v>
@@ -3073,25 +3073,25 @@
         <v>227</v>
       </c>
       <c r="K27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L27" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M27" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="N27" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" t="n">
-        <v>3410.0</v>
+        <v>1872.0</v>
       </c>
       <c r="P27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q27" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="R27" t="e">
         <v>#N/A</v>
@@ -3327,7 +3327,7 @@
         <v>253</v>
       </c>
       <c r="Q31" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R31" t="e">
         <v>#N/A</v>
@@ -3368,25 +3368,25 @@
         <v>227</v>
       </c>
       <c r="K32" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L32" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="M32" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N32" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O32" t="n">
-        <v>5454.0</v>
+        <v>58436.0</v>
       </c>
       <c r="P32" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Q32" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="R32" t="e">
         <v>#N/A</v>
@@ -3427,25 +3427,25 @@
         <v>227</v>
       </c>
       <c r="K33" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L33" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="M33" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="O33" t="n">
-        <v>58436.0</v>
+        <v>5212.0</v>
       </c>
       <c r="P33" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q33" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="R33" t="e">
         <v>#N/A</v>
@@ -3486,25 +3486,25 @@
         <v>227</v>
       </c>
       <c r="K34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L34" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>244</v>
+      </c>
+      <c r="N34" t="n">
         <v>0.0</v>
       </c>
-      <c r="M34" t="s">
-        <v>249</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.0</v>
-      </c>
       <c r="O34" t="n">
-        <v>5212.0</v>
+        <v>8868.0</v>
       </c>
       <c r="P34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q34" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="R34" t="e">
         <v>#N/A</v>
@@ -3545,25 +3545,25 @@
         <v>227</v>
       </c>
       <c r="K35" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L35" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M35" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O35" t="n">
-        <v>8868.0</v>
+        <v>5454.0</v>
       </c>
       <c r="P35" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="Q35" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="R35" t="e">
         <v>#N/A</v>
@@ -3622,7 +3622,7 @@
         <v>258</v>
       </c>
       <c r="Q36" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R36" t="e">
         <v>#N/A</v>
@@ -4135,25 +4135,25 @@
         <v>227</v>
       </c>
       <c r="K45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L45" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M45" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="N45" t="n">
         <v>1.0</v>
       </c>
       <c r="O45" t="n">
-        <v>8402.0</v>
+        <v>6111.0</v>
       </c>
       <c r="P45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q45" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="R45" t="e">
         <v>#N/A</v>
@@ -4194,25 +4194,25 @@
         <v>227</v>
       </c>
       <c r="K46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L46" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>249</v>
+      </c>
+      <c r="N46" t="n">
         <v>0.0</v>
       </c>
-      <c r="M46" t="s">
-        <v>242</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O46" t="n">
-        <v>6111.0</v>
+        <v>60411.0</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q46" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="R46" t="e">
         <v>#N/A</v>
@@ -4271,7 +4271,7 @@
         <v>260</v>
       </c>
       <c r="Q47" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="R47" t="e">
         <v>#N/A</v>
@@ -4312,25 +4312,25 @@
         <v>227</v>
       </c>
       <c r="K48" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L48" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O48" t="n">
-        <v>60411.0</v>
+        <v>8402.0</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q48" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="R48" t="e">
         <v>#N/A</v>
@@ -4430,25 +4430,25 @@
         <v>227</v>
       </c>
       <c r="K50" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L50" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M50" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="N50" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="O50" t="n">
-        <v>4001.0</v>
+        <v>14885.0</v>
       </c>
       <c r="P50" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R50" t="e">
         <v>#N/A</v>
@@ -4489,25 +4489,25 @@
         <v>227</v>
       </c>
       <c r="K51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="L51" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>244</v>
+      </c>
+      <c r="N51" t="n">
         <v>3.0</v>
       </c>
-      <c r="M51" t="s">
-        <v>247</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O51" t="n">
-        <v>14885.0</v>
+        <v>4001.0</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="R51" t="e">
         <v>#N/A</v>
@@ -4861,7 +4861,7 @@
         <v>260</v>
       </c>
       <c r="Q57" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R57" t="e">
         <v>#N/A</v>
@@ -5256,25 +5256,25 @@
         <v>227</v>
       </c>
       <c r="K64" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L64" t="n">
         <v>4.0</v>
       </c>
       <c r="M64" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N64" t="n">
         <v>0.0</v>
       </c>
       <c r="O64" t="n">
-        <v>6846.0</v>
+        <v>58687.0</v>
       </c>
       <c r="P64" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Q64" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="R64" t="e">
         <v>#N/A</v>
@@ -5315,25 +5315,25 @@
         <v>227</v>
       </c>
       <c r="K65" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L65" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="M65" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="O65" t="n">
-        <v>58687.0</v>
+        <v>5207.0</v>
       </c>
       <c r="P65" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q65" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="R65" t="e">
         <v>#N/A</v>
@@ -5374,25 +5374,25 @@
         <v>227</v>
       </c>
       <c r="K66" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L66" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="M66" t="s">
+        <v>248</v>
+      </c>
+      <c r="N66" t="n">
         <v>0.0</v>
       </c>
-      <c r="M66" t="s">
-        <v>247</v>
-      </c>
-      <c r="N66" t="n">
-        <v>3.0</v>
-      </c>
       <c r="O66" t="n">
-        <v>5207.0</v>
+        <v>6846.0</v>
       </c>
       <c r="P66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q66" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="R66" t="e">
         <v>#N/A</v>
@@ -5964,25 +5964,25 @@
         <v>227</v>
       </c>
       <c r="K76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L76" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M76" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="N76" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O76" t="n">
-        <v>4994.0</v>
+        <v>19265.0</v>
       </c>
       <c r="P76" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q76" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="R76" t="e">
         <v>#N/A</v>
@@ -6082,25 +6082,25 @@
         <v>227</v>
       </c>
       <c r="K78" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L78" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M78" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="N78" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O78" t="n">
-        <v>19265.0</v>
+        <v>4994.0</v>
       </c>
       <c r="P78" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q78" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="R78" t="e">
         <v>#N/A</v>
@@ -6200,25 +6200,25 @@
         <v>227</v>
       </c>
       <c r="K80" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L80" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M80" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N80" t="n">
         <v>0.0</v>
       </c>
       <c r="O80" t="n">
-        <v>51065.0</v>
+        <v>6603.0</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q80" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="R80" t="e">
         <v>#N/A</v>
@@ -6259,25 +6259,25 @@
         <v>227</v>
       </c>
       <c r="K81" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="L81" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M81" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N81" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O81" t="n">
-        <v>6287.0</v>
+        <v>51065.0</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q81" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="R81" t="e">
         <v>#N/A</v>
@@ -6318,25 +6318,25 @@
         <v>227</v>
       </c>
       <c r="K82" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L82" t="n">
         <v>1.0</v>
       </c>
       <c r="M82" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N82" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O82" t="n">
-        <v>18715.0</v>
+        <v>17007.0</v>
       </c>
       <c r="P82" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="Q82" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="R82" t="e">
         <v>#N/A</v>
@@ -6377,25 +6377,25 @@
         <v>227</v>
       </c>
       <c r="K83" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L83" t="n">
         <v>1.0</v>
       </c>
       <c r="M83" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N83" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O83" t="n">
-        <v>17007.0</v>
+        <v>18715.0</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Q83" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="R83" t="e">
         <v>#N/A</v>
@@ -6436,25 +6436,25 @@
         <v>227</v>
       </c>
       <c r="K84" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="L84" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M84" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="N84" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O84" t="n">
-        <v>6603.0</v>
+        <v>6287.0</v>
       </c>
       <c r="P84" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Q84" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="R84" t="e">
         <v>#N/A</v>
@@ -6513,7 +6513,7 @@
         <v>263</v>
       </c>
       <c r="Q85" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R85" t="e">
         <v>#N/A</v>
@@ -6672,25 +6672,25 @@
         <v>227</v>
       </c>
       <c r="K88" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="L88" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M88" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="N88" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O88" t="n">
-        <v>58838.0</v>
+        <v>5426.0</v>
       </c>
       <c r="P88" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q88" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R88" t="e">
         <v>#N/A</v>
@@ -6731,25 +6731,25 @@
         <v>227</v>
       </c>
       <c r="K89" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L89" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M89" t="s">
+        <v>244</v>
+      </c>
+      <c r="N89" t="n">
         <v>0.0</v>
       </c>
-      <c r="M89" t="s">
-        <v>241</v>
-      </c>
-      <c r="N89" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O89" t="n">
-        <v>10214.0</v>
+        <v>58838.0</v>
       </c>
       <c r="P89" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q89" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="R89" t="e">
         <v>#N/A</v>
@@ -6790,25 +6790,25 @@
         <v>227</v>
       </c>
       <c r="K90" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="L90" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M90" t="s">
+        <v>241</v>
+      </c>
+      <c r="N90" t="n">
         <v>1.0</v>
       </c>
-      <c r="M90" t="s">
-        <v>251</v>
-      </c>
-      <c r="N90" t="n">
-        <v>3.0</v>
-      </c>
       <c r="O90" t="n">
-        <v>5246.0</v>
+        <v>10214.0</v>
       </c>
       <c r="P90" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q90" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="R90" t="e">
         <v>#N/A</v>
@@ -6849,25 +6849,25 @@
         <v>227</v>
       </c>
       <c r="K91" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M91" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="N91" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="O91" t="n">
-        <v>5426.0</v>
+        <v>5246.0</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Q91" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="R91" t="e">
         <v>#N/A</v>
@@ -7144,22 +7144,22 @@
         <v>227</v>
       </c>
       <c r="K96" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="M96" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O96" t="n">
-        <v>17000.0</v>
+        <v>45818.0</v>
       </c>
       <c r="P96" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q96" t="s">
         <v>272</v>
@@ -7203,25 +7203,25 @@
         <v>227</v>
       </c>
       <c r="K97" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L97" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M97" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N97" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O97" t="n">
-        <v>45818.0</v>
+        <v>17000.0</v>
       </c>
       <c r="P97" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Q97" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R97" t="e">
         <v>#N/A</v>
@@ -7262,25 +7262,25 @@
         <v>227</v>
       </c>
       <c r="K98" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M98" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="N98" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="O98" t="n">
-        <v>4003.0</v>
+        <v>15829.0</v>
       </c>
       <c r="P98" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q98" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="R98" t="e">
         <v>#N/A</v>
@@ -7321,25 +7321,25 @@
         <v>227</v>
       </c>
       <c r="K99" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="L99" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M99" t="s">
+        <v>250</v>
+      </c>
+      <c r="N99" t="n">
         <v>2.0</v>
       </c>
-      <c r="M99" t="s">
-        <v>242</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O99" t="n">
-        <v>3892.0</v>
+        <v>18677.0</v>
       </c>
       <c r="P99" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q99" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="R99" t="e">
         <v>#N/A</v>
@@ -7380,25 +7380,25 @@
         <v>227</v>
       </c>
       <c r="K100" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M100" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N100" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="O100" t="n">
-        <v>15829.0</v>
+        <v>3892.0</v>
       </c>
       <c r="P100" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q100" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="R100" t="e">
         <v>#N/A</v>
@@ -7439,25 +7439,25 @@
         <v>227</v>
       </c>
       <c r="K101" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="L101" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M101" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N101" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O101" t="n">
-        <v>18677.0</v>
+        <v>4003.0</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q101" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="R101" t="e">
         <v>#N/A</v>
@@ -7616,25 +7616,25 @@
         <v>227</v>
       </c>
       <c r="K104" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="L104" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M104" t="s">
+        <v>248</v>
+      </c>
+      <c r="N104" t="n">
         <v>0.0</v>
       </c>
-      <c r="M104" t="s">
-        <v>246</v>
-      </c>
-      <c r="N104" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O104" t="n">
-        <v>6298.0</v>
+        <v>16533.0</v>
       </c>
       <c r="P104" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q104" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="R104" t="e">
         <v>#N/A</v>
@@ -7675,25 +7675,25 @@
         <v>227</v>
       </c>
       <c r="K105" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="L105" t="n">
         <v>0.0</v>
       </c>
       <c r="M105" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N105" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="O105" t="n">
-        <v>7458.0</v>
+        <v>6298.0</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="Q105" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="R105" t="e">
         <v>#N/A</v>
@@ -7734,25 +7734,25 @@
         <v>227</v>
       </c>
       <c r="K106" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L106" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M106" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="N106" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="O106" t="n">
-        <v>16533.0</v>
+        <v>7458.0</v>
       </c>
       <c r="P106" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q106" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="R106" t="e">
         <v>#N/A</v>
@@ -7929,7 +7929,7 @@
         <v>264</v>
       </c>
       <c r="Q109" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R109" t="e">
         <v>#N/A</v>
@@ -7970,25 +7970,25 @@
         <v>227</v>
       </c>
       <c r="K110" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="L110" t="n">
         <v>3.0</v>
       </c>
       <c r="M110" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N110" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O110" t="e">
-        <v>#N/A</v>
+        <v>1.0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>5479.0</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R110" t="e">
         <v>#N/A</v>
@@ -8047,7 +8047,7 @@
         <v>263</v>
       </c>
       <c r="Q111" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R111" t="e">
         <v>#N/A</v>
@@ -8147,25 +8147,25 @@
         <v>227</v>
       </c>
       <c r="K113" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L113" t="n">
         <v>3.0</v>
       </c>
       <c r="M113" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N113" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="O113" t="n">
-        <v>5479.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="O113" t="e">
+        <v>#N/A</v>
       </c>
       <c r="P113" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Q113" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R113" t="e">
         <v>#N/A</v>
@@ -8283,7 +8283,7 @@
         <v>256</v>
       </c>
       <c r="Q115" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="R115" t="e">
         <v>#N/A</v>
@@ -8342,7 +8342,7 @@
         <v>261</v>
       </c>
       <c r="Q116" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R116" t="e">
         <v>#N/A</v>
@@ -8383,25 +8383,25 @@
         <v>227</v>
       </c>
       <c r="K117" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L117" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M117" t="s">
+        <v>250</v>
+      </c>
+      <c r="N117" t="n">
         <v>0.0</v>
       </c>
-      <c r="M117" t="s">
-        <v>244</v>
-      </c>
-      <c r="N117" t="n">
-        <v>2.0</v>
-      </c>
       <c r="O117" t="n">
-        <v>49994.0</v>
+        <v>16993.0</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Q117" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="R117" t="e">
         <v>#N/A</v>
@@ -8442,25 +8442,25 @@
         <v>227</v>
       </c>
       <c r="K118" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L118" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M118" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N118" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O118" t="n">
-        <v>4075.0</v>
+        <v>9044.0</v>
       </c>
       <c r="P118" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Q118" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="R118" t="e">
         <v>#N/A</v>
@@ -8501,25 +8501,25 @@
         <v>227</v>
       </c>
       <c r="K119" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="L119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M119" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N119" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O119" t="n">
-        <v>9044.0</v>
+        <v>49994.0</v>
       </c>
       <c r="P119" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="Q119" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="R119" t="e">
         <v>#N/A</v>
@@ -8560,25 +8560,25 @@
         <v>227</v>
       </c>
       <c r="K120" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L120" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M120" t="s">
+        <v>251</v>
+      </c>
+      <c r="N120" t="n">
         <v>1.0</v>
       </c>
-      <c r="M120" t="s">
-        <v>250</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0.0</v>
-      </c>
       <c r="O120" t="n">
-        <v>16993.0</v>
+        <v>4075.0</v>
       </c>
       <c r="P120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q120" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R120" t="e">
         <v>#N/A</v>
@@ -8755,7 +8755,7 @@
         <v>253</v>
       </c>
       <c r="Q123" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R123" t="e">
         <v>#N/A</v>
@@ -8932,7 +8932,7 @@
         <v>254</v>
       </c>
       <c r="Q126" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="R126" t="e">
         <v>#N/A</v>
@@ -9032,25 +9032,25 @@
         <v>227</v>
       </c>
       <c r="K128" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L128" t="n">
         <v>1.0</v>
       </c>
       <c r="M128" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N128" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O128" t="n">
-        <v>50056.0</v>
+        <v>7681.0</v>
       </c>
       <c r="P128" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q128" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="R128" t="e">
         <v>#N/A</v>
@@ -9091,25 +9091,25 @@
         <v>227</v>
       </c>
       <c r="K129" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L129" t="n">
         <v>1.0</v>
       </c>
       <c r="M129" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N129" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O129" t="n">
-        <v>7681.0</v>
+        <v>50056.0</v>
       </c>
       <c r="P129" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q129" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="R129" t="e">
         <v>#N/A</v>
@@ -9270,23 +9270,23 @@
       <c r="K132" t="s">
         <v>249</v>
       </c>
-      <c r="L132" t="e">
-        <v>#N/A</v>
+      <c r="L132" t="n">
+        <v>2.0</v>
       </c>
       <c r="M132" t="s">
         <v>241</v>
       </c>
-      <c r="N132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O132" t="e">
-        <v>#N/A</v>
+      <c r="N132" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>19873.0</v>
       </c>
       <c r="P132" t="s">
         <v>261</v>
       </c>
       <c r="Q132" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="R132" t="e">
         <v>#N/A</v>
@@ -9329,23 +9329,23 @@
       <c r="K133" t="s">
         <v>248</v>
       </c>
-      <c r="L133" t="e">
-        <v>#N/A</v>
+      <c r="L133" t="n">
+        <v>2.0</v>
       </c>
       <c r="M133" t="s">
         <v>243</v>
       </c>
-      <c r="N133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O133" t="e">
-        <v>#N/A</v>
+      <c r="N133" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>17862.0</v>
       </c>
       <c r="P133" t="s">
         <v>260</v>
       </c>
       <c r="Q133" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R133" t="e">
         <v>#N/A</v>
@@ -9622,22 +9622,22 @@
         <v>227</v>
       </c>
       <c r="K138" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="L138" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M138" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="N138" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O138" t="n">
-        <v>16146.0</v>
+        <v>6895.0</v>
       </c>
       <c r="P138" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="Q138" t="s">
         <v>266</v>
@@ -9681,22 +9681,22 @@
         <v>227</v>
       </c>
       <c r="K139" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="L139" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M139" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="N139" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O139" t="n">
-        <v>6895.0</v>
+        <v>16146.0</v>
       </c>
       <c r="P139" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q139" t="s">
         <v>266</v>
@@ -9740,25 +9740,25 @@
         <v>227</v>
       </c>
       <c r="K140" t="s">
-        <v>242</v>
-      </c>
-      <c r="L140" t="e">
-        <v>#N/A</v>
+        <v>241</v>
+      </c>
+      <c r="L140" t="n">
+        <v>2.0</v>
       </c>
       <c r="M140" t="s">
-        <v>244</v>
-      </c>
-      <c r="N140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O140" t="e">
-        <v>#N/A</v>
+        <v>247</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>18648.0</v>
       </c>
       <c r="P140" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q140" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="R140" t="e">
         <v>#N/A</v>
@@ -9799,25 +9799,25 @@
         <v>227</v>
       </c>
       <c r="K141" t="s">
-        <v>246</v>
-      </c>
-      <c r="L141" t="e">
-        <v>#N/A</v>
+        <v>250</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1.0</v>
       </c>
       <c r="M141" t="s">
-        <v>248</v>
-      </c>
-      <c r="N141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O141" t="e">
-        <v>#N/A</v>
+        <v>249</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>6703.0</v>
       </c>
       <c r="P141" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q141" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="R141" t="e">
         <v>#N/A</v>
@@ -9858,25 +9858,25 @@
         <v>227</v>
       </c>
       <c r="K142" t="s">
-        <v>250</v>
-      </c>
-      <c r="L142" t="e">
-        <v>#N/A</v>
+        <v>246</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.0</v>
       </c>
       <c r="M142" t="s">
-        <v>249</v>
-      </c>
-      <c r="N142" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O142" t="e">
-        <v>#N/A</v>
+        <v>248</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>7733.0</v>
       </c>
       <c r="P142" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Q142" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="R142" t="e">
         <v>#N/A</v>
@@ -9917,25 +9917,25 @@
         <v>227</v>
       </c>
       <c r="K143" t="s">
-        <v>241</v>
-      </c>
-      <c r="L143" t="e">
-        <v>#N/A</v>
+        <v>242</v>
+      </c>
+      <c r="L143" t="n">
+        <v>2.0</v>
       </c>
       <c r="M143" t="s">
-        <v>247</v>
-      </c>
-      <c r="N143" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O143" t="e">
-        <v>#N/A</v>
+        <v>244</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>6121.0</v>
       </c>
       <c r="P143" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q143" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="R143" t="e">
         <v>#N/A</v>
@@ -9978,14 +9978,14 @@
       <c r="K144" t="s">
         <v>245</v>
       </c>
-      <c r="L144" t="e">
-        <v>#N/A</v>
+      <c r="L144" t="n">
+        <v>2.0</v>
       </c>
       <c r="M144" t="s">
         <v>252</v>
       </c>
-      <c r="N144" t="e">
-        <v>#N/A</v>
+      <c r="N144" t="n">
+        <v>3.0</v>
       </c>
       <c r="O144" t="e">
         <v>#N/A</v>
@@ -9994,7 +9994,7 @@
         <v>257</v>
       </c>
       <c r="Q144" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R144" t="e">
         <v>#N/A</v>
@@ -10037,23 +10037,23 @@
       <c r="K145" t="s">
         <v>243</v>
       </c>
-      <c r="L145" t="e">
-        <v>#N/A</v>
+      <c r="L145" t="n">
+        <v>2.0</v>
       </c>
       <c r="M145" t="s">
         <v>251</v>
       </c>
-      <c r="N145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O145" t="e">
-        <v>#N/A</v>
+      <c r="N145" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>13000.0</v>
       </c>
       <c r="P145" t="s">
         <v>255</v>
       </c>
       <c r="Q145" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="R145" t="e">
         <v>#N/A</v>
@@ -10094,13 +10094,13 @@
         <v>227</v>
       </c>
       <c r="K146" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L146" t="e">
         <v>#N/A</v>
       </c>
       <c r="M146" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="N146" t="e">
         <v>#N/A</v>
@@ -10109,7 +10109,7 @@
         <v>#N/A</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q146" t="s">
         <v>266</v>
@@ -10153,13 +10153,13 @@
         <v>227</v>
       </c>
       <c r="K147" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L147" t="e">
         <v>#N/A</v>
       </c>
       <c r="M147" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N147" t="e">
         <v>#N/A</v>
@@ -10168,7 +10168,7 @@
         <v>#N/A</v>
       </c>
       <c r="P147" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q147" t="s">
         <v>266</v>
@@ -10212,13 +10212,13 @@
         <v>227</v>
       </c>
       <c r="K148" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="L148" t="e">
         <v>#N/A</v>
       </c>
       <c r="M148" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N148" t="e">
         <v>#N/A</v>
@@ -10227,7 +10227,7 @@
         <v>#N/A</v>
       </c>
       <c r="P148" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q148" t="s">
         <v>266</v>
@@ -10327,7 +10327,7 @@
         <v>45745.0</v>
       </c>
       <c r="J150" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K150" t="s">
         <v>251</v>
@@ -10380,22 +10380,22 @@
         <v>48</v>
       </c>
       <c r="H151" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I151" t="n" s="2">
-        <v>45745.0</v>
+        <v>45746.0</v>
       </c>
       <c r="J151" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="K151" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L151" t="e">
         <v>#N/A</v>
       </c>
       <c r="M151" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N151" t="e">
         <v>#N/A</v>
@@ -10404,7 +10404,7 @@
         <v>#N/A</v>
       </c>
       <c r="P151" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q151" t="s">
         <v>266</v>
@@ -10448,13 +10448,13 @@
         <v>227</v>
       </c>
       <c r="K152" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L152" t="e">
         <v>#N/A</v>
       </c>
       <c r="M152" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="N152" t="e">
         <v>#N/A</v>
@@ -10463,7 +10463,7 @@
         <v>#N/A</v>
       </c>
       <c r="P152" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q152" t="s">
         <v>266</v>
@@ -10507,13 +10507,13 @@
         <v>227</v>
       </c>
       <c r="K153" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="L153" t="e">
         <v>#N/A</v>
       </c>
       <c r="M153" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N153" t="e">
         <v>#N/A</v>
@@ -10522,7 +10522,7 @@
         <v>#N/A</v>
       </c>
       <c r="P153" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q153" t="s">
         <v>266</v>
@@ -10566,13 +10566,13 @@
         <v>227</v>
       </c>
       <c r="K154" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L154" t="e">
         <v>#N/A</v>
       </c>
       <c r="M154" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N154" t="e">
         <v>#N/A</v>
@@ -10581,7 +10581,7 @@
         <v>#N/A</v>
       </c>
       <c r="P154" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q154" t="s">
         <v>266</v>
@@ -10625,13 +10625,13 @@
         <v>227</v>
       </c>
       <c r="K155" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="L155" t="e">
         <v>#N/A</v>
       </c>
       <c r="M155" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="N155" t="e">
         <v>#N/A</v>
@@ -10640,7 +10640,7 @@
         <v>#N/A</v>
       </c>
       <c r="P155" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q155" t="s">
         <v>266</v>
@@ -10675,22 +10675,22 @@
         <v>49</v>
       </c>
       <c r="H156" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I156" t="n" s="2">
-        <v>45752.0</v>
+        <v>45753.0</v>
       </c>
       <c r="J156" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K156" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="L156" t="e">
         <v>#N/A</v>
       </c>
       <c r="M156" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N156" t="e">
         <v>#N/A</v>
@@ -10699,7 +10699,7 @@
         <v>#N/A</v>
       </c>
       <c r="P156" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q156" t="s">
         <v>266</v>
@@ -10734,22 +10734,22 @@
         <v>49</v>
       </c>
       <c r="H157" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I157" t="n" s="2">
-        <v>45752.0</v>
+        <v>45753.0</v>
       </c>
       <c r="J157" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="K157" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="L157" t="e">
         <v>#N/A</v>
       </c>
       <c r="M157" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N157" t="e">
         <v>#N/A</v>
@@ -10758,7 +10758,7 @@
         <v>#N/A</v>
       </c>
       <c r="P157" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="Q157" t="s">
         <v>266</v>
@@ -10802,13 +10802,13 @@
         <v>227</v>
       </c>
       <c r="K158" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L158" t="e">
         <v>#N/A</v>
       </c>
       <c r="M158" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N158" t="e">
         <v>#N/A</v>
@@ -10817,7 +10817,7 @@
         <v>#N/A</v>
       </c>
       <c r="P158" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q158" t="s">
         <v>266</v>
@@ -10861,13 +10861,13 @@
         <v>227</v>
       </c>
       <c r="K159" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="L159" t="e">
         <v>#N/A</v>
       </c>
       <c r="M159" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N159" t="e">
         <v>#N/A</v>
@@ -10876,7 +10876,7 @@
         <v>#N/A</v>
       </c>
       <c r="P159" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q159" t="s">
         <v>266</v>
@@ -10920,13 +10920,13 @@
         <v>227</v>
       </c>
       <c r="K160" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L160" t="e">
         <v>#N/A</v>
       </c>
       <c r="M160" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N160" t="e">
         <v>#N/A</v>
@@ -10935,7 +10935,7 @@
         <v>#N/A</v>
       </c>
       <c r="P160" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q160" t="s">
         <v>266</v>
@@ -10979,13 +10979,13 @@
         <v>227</v>
       </c>
       <c r="K161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L161" t="e">
         <v>#N/A</v>
       </c>
       <c r="M161" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N161" t="e">
         <v>#N/A</v>
@@ -10994,7 +10994,7 @@
         <v>#N/A</v>
       </c>
       <c r="P161" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q161" t="s">
         <v>266</v>
@@ -11029,22 +11029,22 @@
         <v>50</v>
       </c>
       <c r="H162" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I162" t="n" s="2">
-        <v>45759.0</v>
+        <v>45760.0</v>
       </c>
       <c r="J162" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K162" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L162" t="e">
         <v>#N/A</v>
       </c>
       <c r="M162" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N162" t="e">
         <v>#N/A</v>
@@ -11053,7 +11053,7 @@
         <v>#N/A</v>
       </c>
       <c r="P162" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q162" t="s">
         <v>266</v>
@@ -11088,22 +11088,22 @@
         <v>50</v>
       </c>
       <c r="H163" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I163" t="n" s="2">
-        <v>45759.0</v>
+        <v>45760.0</v>
       </c>
       <c r="J163" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="K163" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="L163" t="e">
         <v>#N/A</v>
       </c>
       <c r="M163" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="N163" t="e">
         <v>#N/A</v>
@@ -11112,7 +11112,7 @@
         <v>#N/A</v>
       </c>
       <c r="P163" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q163" t="s">
         <v>266</v>
@@ -11156,25 +11156,25 @@
         <v>227</v>
       </c>
       <c r="K164" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="L164" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M164" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N164" t="n">
         <v>2.0</v>
       </c>
       <c r="O164" t="n">
-        <v>5779.0</v>
+        <v>3629.0</v>
       </c>
       <c r="P164" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q164" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="R164" t="e">
         <v>#N/A</v>
@@ -11215,25 +11215,25 @@
         <v>227</v>
       </c>
       <c r="K165" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="L165" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M165" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N165" t="n">
         <v>2.0</v>
       </c>
       <c r="O165" t="n">
-        <v>3629.0</v>
+        <v>5779.0</v>
       </c>
       <c r="P165" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q165" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="R165" t="e">
         <v>#N/A</v>
@@ -11292,7 +11292,7 @@
         <v>259</v>
       </c>
       <c r="Q166" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R166" t="e">
         <v>#N/A</v>
@@ -11392,25 +11392,25 @@
         <v>227</v>
       </c>
       <c r="K168" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="L168" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M168" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="N168" t="n">
         <v>1.0</v>
       </c>
       <c r="O168" t="n">
-        <v>18648.0</v>
+        <v>7763.0</v>
       </c>
       <c r="P168" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="Q168" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="R168" t="e">
         <v>#N/A</v>
@@ -11451,25 +11451,25 @@
         <v>227</v>
       </c>
       <c r="K169" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="L169" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M169" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N169" t="n">
         <v>1.0</v>
       </c>
       <c r="O169" t="n">
-        <v>7763.0</v>
+        <v>18648.0</v>
       </c>
       <c r="P169" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="Q169" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="R169" t="e">
         <v>#N/A</v>
@@ -11510,25 +11510,25 @@
         <v>227</v>
       </c>
       <c r="K170" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L170" t="n">
         <v>2.0</v>
       </c>
       <c r="M170" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N170" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O170" t="n">
-        <v>6957.0</v>
+        <v>4068.0</v>
       </c>
       <c r="P170" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q170" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="R170" t="e">
         <v>#N/A</v>
@@ -11628,25 +11628,25 @@
         <v>227</v>
       </c>
       <c r="K172" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L172" t="n">
         <v>2.0</v>
       </c>
       <c r="M172" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="N172" t="n">
         <v>0.0</v>
       </c>
       <c r="O172" t="n">
-        <v>4068.0</v>
+        <v>15448.0</v>
       </c>
       <c r="P172" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q172" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="R172" t="e">
         <v>#N/A</v>
@@ -11687,25 +11687,25 @@
         <v>227</v>
       </c>
       <c r="K173" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L173" t="n">
         <v>2.0</v>
       </c>
       <c r="M173" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N173" t="n">
         <v>0.0</v>
       </c>
       <c r="O173" t="n">
-        <v>15448.0</v>
+        <v>58872.0</v>
       </c>
       <c r="P173" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Q173" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="R173" t="e">
         <v>#N/A</v>
@@ -11746,25 +11746,25 @@
         <v>227</v>
       </c>
       <c r="K174" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L174" t="n">
         <v>2.0</v>
       </c>
       <c r="M174" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="N174" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O174" t="n">
-        <v>58872.0</v>
+        <v>6957.0</v>
       </c>
       <c r="P174" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q174" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="R174" t="e">
         <v>#N/A</v>
@@ -11864,25 +11864,25 @@
         <v>227</v>
       </c>
       <c r="K176" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="L176" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M176" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N176" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="O176" t="n">
-        <v>18399.0</v>
+        <v>6257.0</v>
       </c>
       <c r="P176" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="Q176" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="R176" t="e">
         <v>#N/A</v>
@@ -11923,25 +11923,25 @@
         <v>227</v>
       </c>
       <c r="K177" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="L177" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M177" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="N177" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="O177" t="n">
-        <v>6257.0</v>
+        <v>18399.0</v>
       </c>
       <c r="P177" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="Q177" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="R177" t="e">
         <v>#N/A</v>
@@ -11982,25 +11982,25 @@
         <v>227</v>
       </c>
       <c r="K178" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="L178" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M178" t="s">
+        <v>248</v>
+      </c>
+      <c r="N178" t="n">
         <v>2.0</v>
       </c>
-      <c r="M178" t="s">
-        <v>244</v>
-      </c>
-      <c r="N178" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O178" t="n">
-        <v>5214.0</v>
+        <v>9030.0</v>
       </c>
       <c r="P178" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Q178" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="R178" t="e">
         <v>#N/A</v>
@@ -12041,25 +12041,25 @@
         <v>227</v>
       </c>
       <c r="K179" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="L179" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M179" t="s">
+        <v>244</v>
+      </c>
+      <c r="N179" t="n">
         <v>1.0</v>
       </c>
-      <c r="M179" t="s">
-        <v>248</v>
-      </c>
-      <c r="N179" t="n">
-        <v>2.0</v>
-      </c>
       <c r="O179" t="n">
-        <v>9030.0</v>
+        <v>5214.0</v>
       </c>
       <c r="P179" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="Q179" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="R179" t="e">
         <v>#N/A</v>
@@ -12218,25 +12218,25 @@
         <v>227</v>
       </c>
       <c r="K182" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="L182" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M182" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="N182" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="O182" t="n">
-        <v>17106.0</v>
+        <v>5316.0</v>
       </c>
       <c r="P182" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="Q182" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="R182" t="e">
         <v>#N/A</v>
@@ -12277,25 +12277,25 @@
         <v>227</v>
       </c>
       <c r="K183" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L183" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M183" t="s">
+        <v>243</v>
+      </c>
+      <c r="N183" t="n">
         <v>1.0</v>
       </c>
-      <c r="M183" t="s">
-        <v>242</v>
-      </c>
-      <c r="N183" t="n">
-        <v>2.0</v>
-      </c>
       <c r="O183" t="n">
-        <v>5316.0</v>
+        <v>17106.0</v>
       </c>
       <c r="P183" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q183" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="R183" t="e">
         <v>#N/A</v>
@@ -12336,25 +12336,25 @@
         <v>227</v>
       </c>
       <c r="K184" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L184" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M184" t="s">
+        <v>242</v>
+      </c>
+      <c r="N184" t="n">
         <v>2.0</v>
-      </c>
-      <c r="M184" t="s">
-        <v>250</v>
-      </c>
-      <c r="N184" t="n">
-        <v>3.0</v>
       </c>
       <c r="O184" t="n">
         <v>5316.0</v>
       </c>
       <c r="P184" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q184" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="R184" t="e">
         <v>#N/A</v>
@@ -12572,25 +12572,25 @@
         <v>227</v>
       </c>
       <c r="K188" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="L188" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M188" t="s">
+        <v>247</v>
+      </c>
+      <c r="N188" t="n">
         <v>0.0</v>
       </c>
-      <c r="M188" t="s">
-        <v>251</v>
-      </c>
-      <c r="N188" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O188" t="n">
-        <v>5084.0</v>
+        <v>3688.0</v>
       </c>
       <c r="P188" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q188" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="R188" t="e">
         <v>#N/A</v>
@@ -12631,25 +12631,25 @@
         <v>227</v>
       </c>
       <c r="K189" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="L189" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M189" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N189" t="n">
         <v>0.0</v>
       </c>
       <c r="O189" t="n">
-        <v>3688.0</v>
+        <v>18757.0</v>
       </c>
       <c r="P189" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q189" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="R189" t="e">
         <v>#N/A</v>
@@ -12690,25 +12690,25 @@
         <v>227</v>
       </c>
       <c r="K190" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L190" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M190" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N190" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O190" t="n">
-        <v>18757.0</v>
+        <v>58890.0</v>
       </c>
       <c r="P190" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q190" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="R190" t="e">
         <v>#N/A</v>
@@ -12749,25 +12749,25 @@
         <v>227</v>
       </c>
       <c r="K191" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L191" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M191" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N191" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O191" t="n">
-        <v>58890.0</v>
+        <v>5084.0</v>
       </c>
       <c r="P191" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q191" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="R191" t="e">
         <v>#N/A</v>
@@ -12885,7 +12885,7 @@
         <v>262</v>
       </c>
       <c r="Q193" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R193" t="e">
         <v>#N/A</v>
@@ -12926,25 +12926,25 @@
         <v>227</v>
       </c>
       <c r="K194" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L194" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M194" t="s">
+        <v>250</v>
+      </c>
+      <c r="N194" t="n">
         <v>1.0</v>
       </c>
-      <c r="M194" t="s">
-        <v>246</v>
-      </c>
-      <c r="N194" t="n">
-        <v>2.0</v>
-      </c>
       <c r="O194" t="n">
-        <v>6548.0</v>
+        <v>3419.0</v>
       </c>
       <c r="P194" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="Q194" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="R194" t="e">
         <v>#N/A</v>
@@ -12985,25 +12985,25 @@
         <v>227</v>
       </c>
       <c r="K195" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="L195" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M195" t="s">
+        <v>246</v>
+      </c>
+      <c r="N195" t="n">
         <v>2.0</v>
       </c>
-      <c r="M195" t="s">
-        <v>250</v>
-      </c>
-      <c r="N195" t="n">
-        <v>1.0</v>
-      </c>
       <c r="O195" t="n">
-        <v>3419.0</v>
+        <v>6548.0</v>
       </c>
       <c r="P195" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q195" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="R195" t="e">
         <v>#N/A</v>
@@ -13062,7 +13062,7 @@
         <v>260</v>
       </c>
       <c r="Q196" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="R196" t="e">
         <v>#N/A</v>
